--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5457"/>
+  <dimension ref="A1:B5460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55000,6 +55000,36 @@
         <v>2.34</v>
       </c>
     </row>
+    <row r="5458">
+      <c r="A5458" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B5458" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="5459">
+      <c r="A5459" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B5459" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="5460">
+      <c r="A5460" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B5460" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5460"/>
+  <dimension ref="A1:B5463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55030,6 +55030,36 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="5461">
+      <c r="A5461" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B5461" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="5462">
+      <c r="A5462" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B5462" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="5463">
+      <c r="A5463" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B5463" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5463"/>
+  <dimension ref="A1:B5464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55060,6 +55060,16 @@
         <v>2.4</v>
       </c>
     </row>
+    <row r="5464">
+      <c r="A5464" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B5464" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5464"/>
+  <dimension ref="A1:B5467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55070,6 +55070,36 @@
         <v>2.38</v>
       </c>
     </row>
+    <row r="5465">
+      <c r="A5465" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B5465" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="5466">
+      <c r="A5466" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B5466" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="5467">
+      <c r="A5467" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B5467" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5467"/>
+  <dimension ref="A1:B5473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55100,6 +55100,66 @@
         <v>2.37</v>
       </c>
     </row>
+    <row r="5468">
+      <c r="A5468" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B5468" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="5469">
+      <c r="A5469" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5469" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="5470">
+      <c r="A5470" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B5470" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="5471">
+      <c r="A5471" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B5471" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="5472">
+      <c r="A5472" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B5472" t="n">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="5473">
+      <c r="A5473" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B5473" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5473"/>
+  <dimension ref="A1:B5477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55160,6 +55160,46 @@
         <v>2.45</v>
       </c>
     </row>
+    <row r="5474">
+      <c r="A5474" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B5474" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="5475">
+      <c r="A5475" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B5475" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="5476">
+      <c r="A5476" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B5476" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="5477">
+      <c r="A5477" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B5477" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5477"/>
+  <dimension ref="A1:B5478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55200,6 +55200,16 @@
         <v>2.28</v>
       </c>
     </row>
+    <row r="5478">
+      <c r="A5478" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B5478" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5478"/>
+  <dimension ref="A1:B5481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55210,6 +55210,36 @@
         <v>2.28</v>
       </c>
     </row>
+    <row r="5479">
+      <c r="A5479" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B5479" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="5480">
+      <c r="A5480" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B5480" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="5481">
+      <c r="A5481" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B5481" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5481"/>
+  <dimension ref="A1:B5483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55240,6 +55240,26 @@
         <v>2.19</v>
       </c>
     </row>
+    <row r="5482">
+      <c r="A5482" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B5482" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="5483">
+      <c r="A5483" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B5483" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5483"/>
+  <dimension ref="A1:B5484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55260,6 +55260,16 @@
         <v>2.26</v>
       </c>
     </row>
+    <row r="5484">
+      <c r="A5484" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B5484" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5484"/>
+  <dimension ref="A1:B5486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55270,6 +55270,26 @@
         <v>2.25</v>
       </c>
     </row>
+    <row r="5485">
+      <c r="A5485" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B5485" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="5486">
+      <c r="A5486" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B5486" t="n">
+        <v>2.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5486"/>
+  <dimension ref="A1:B5488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55290,6 +55290,26 @@
         <v>2.12</v>
       </c>
     </row>
+    <row r="5487">
+      <c r="A5487" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B5487" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="5488">
+      <c r="A5488" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B5488" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5488"/>
+  <dimension ref="A1:B5490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55310,6 +55310,26 @@
         <v>1.93</v>
       </c>
     </row>
+    <row r="5489">
+      <c r="A5489" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B5489" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="5490">
+      <c r="A5490" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B5490" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5490"/>
+  <dimension ref="A1:B5491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55330,6 +55330,16 @@
         <v>1.89</v>
       </c>
     </row>
+    <row r="5491">
+      <c r="A5491" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B5491" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5491"/>
+  <dimension ref="A1:B5492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55340,6 +55340,16 @@
         <v>1.82</v>
       </c>
     </row>
+    <row r="5492">
+      <c r="A5492" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B5492" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5492"/>
+  <dimension ref="A1:B5497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55350,6 +55350,56 @@
         <v>1.6</v>
       </c>
     </row>
+    <row r="5493">
+      <c r="A5493" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B5493" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="5494">
+      <c r="A5494" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B5494" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="5495">
+      <c r="A5495" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B5495" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="5496">
+      <c r="A5496" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B5496" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="5497">
+      <c r="A5497" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B5497" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5497"/>
+  <dimension ref="A1:B5501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55400,6 +55400,46 @@
         <v>1.71</v>
       </c>
     </row>
+    <row r="5498">
+      <c r="A5498" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B5498" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="5499">
+      <c r="A5499" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B5499" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="5500">
+      <c r="A5500" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B5500" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="5501">
+      <c r="A5501" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B5501" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5501"/>
+  <dimension ref="A1:B5505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55440,6 +55440,46 @@
         <v>1.72</v>
       </c>
     </row>
+    <row r="5502">
+      <c r="A5502" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B5502" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="5503">
+      <c r="A5503" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B5503" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="5504">
+      <c r="A5504" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B5504" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="5505">
+      <c r="A5505" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B5505" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5505"/>
+  <dimension ref="A1:B5506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55480,6 +55480,16 @@
         <v>1.63</v>
       </c>
     </row>
+    <row r="5506">
+      <c r="A5506" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B5506" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5506"/>
+  <dimension ref="A1:B5509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55490,6 +55490,36 @@
         <v>1.63</v>
       </c>
     </row>
+    <row r="5507">
+      <c r="A5507" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B5507" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="5508">
+      <c r="A5508" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B5508" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="5509">
+      <c r="A5509" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B5509" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5509"/>
+  <dimension ref="A1:B5511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55520,6 +55520,26 @@
         <v>1.64</v>
       </c>
     </row>
+    <row r="5510">
+      <c r="A5510" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B5510" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="5511">
+      <c r="A5511" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B5511" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5511"/>
+  <dimension ref="A1:B5512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55540,6 +55540,16 @@
         <v>1.54</v>
       </c>
     </row>
+    <row r="5512">
+      <c r="A5512" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B5512" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5512"/>
+  <dimension ref="A1:B5514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55550,6 +55550,26 @@
         <v>1.64</v>
       </c>
     </row>
+    <row r="5513">
+      <c r="A5513" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B5513" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="5514">
+      <c r="A5514" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B5514" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5514"/>
+  <dimension ref="A1:B5517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55570,6 +55570,36 @@
         <v>1.58</v>
       </c>
     </row>
+    <row r="5515">
+      <c r="A5515" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B5515" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="5516">
+      <c r="A5516" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B5516" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="5517">
+      <c r="A5517" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B5517" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5517"/>
+  <dimension ref="A1:B5520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55600,6 +55600,36 @@
         <v>1.64</v>
       </c>
     </row>
+    <row r="5518">
+      <c r="A5518" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B5518" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="5519">
+      <c r="A5519" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B5519" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="5520">
+      <c r="A5520" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B5520" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5520"/>
+  <dimension ref="A1:B5522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55630,6 +55630,26 @@
         <v>1.69</v>
       </c>
     </row>
+    <row r="5521">
+      <c r="A5521" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B5521" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="5522">
+      <c r="A5522" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B5522" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5522"/>
+  <dimension ref="A1:B5529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55650,6 +55650,76 @@
         <v>1.59</v>
       </c>
     </row>
+    <row r="5523">
+      <c r="A5523" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B5523" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="5524">
+      <c r="A5524" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B5524" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="5525">
+      <c r="A5525" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B5525" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="5526">
+      <c r="A5526" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B5526" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="5527">
+      <c r="A5527" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B5527" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="5528">
+      <c r="A5528" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B5528" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="5529">
+      <c r="A5529" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B5529" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz_lth.xlsx
+++ b/data_cripto/btc_mvrvz_lth.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5529"/>
+  <dimension ref="A1:B5535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55720,6 +55720,66 @@
         <v>1.69</v>
       </c>
     </row>
+    <row r="5530">
+      <c r="A5530" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B5530" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="5531">
+      <c r="A5531" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B5531" t="n">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="5532">
+      <c r="A5532" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B5532" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="5533">
+      <c r="A5533" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B5533" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="5534">
+      <c r="A5534" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B5534" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="5535">
+      <c r="A5535" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5535" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
